--- a/data/gravel/Giant Revolt X pro 1 long 2025.xlsx
+++ b/data/gravel/Giant Revolt X pro 1 long 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel copy/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F30C78C-0CF1-5D4C-8157-711D87951554}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CD87513-1CDC-8F4D-B81B-BCF07AA38BA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="26480" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11060" yWindow="1320" windowWidth="26480" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="109">
   <si>
     <t>brand</t>
   </si>
@@ -304,9 +304,6 @@
     <t>no</t>
   </si>
   <si>
-    <t>pf</t>
-  </si>
-  <si>
     <t>frame_weight</t>
   </si>
   <si>
@@ -331,7 +328,25 @@
     <t>fork</t>
   </si>
   <si>
-    <t>rigid</t>
+    <t>flip</t>
+  </si>
+  <si>
+    <t>internal</t>
+  </si>
+  <si>
+    <t>usd</t>
+  </si>
+  <si>
+    <t>suspension</t>
+  </si>
+  <si>
+    <t>press fit</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>https://www.giant-bicycles.com/discover/en-us/gravel-cycling/gravel/revolt-x</t>
   </si>
 </sst>
 </file>
@@ -371,9 +386,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -704,21 +720,24 @@
       <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="s">
-        <v>5</v>
+      <c r="B4" s="2">
+        <v>45888</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>7</v>
       </c>
+      <c r="B5" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -726,7 +745,7 @@
         <v>9</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C8" t="s">
         <v>10</v>
@@ -1165,7 +1184,7 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
@@ -1334,26 +1353,26 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>97</v>
+      </c>
+      <c r="B34" t="s">
         <v>98</v>
-      </c>
-      <c r="B34" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>99</v>
+      </c>
+      <c r="B35" t="s">
         <v>100</v>
-      </c>
-      <c r="B35" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>102</v>
-      </c>
-      <c r="B36" t="s">
-        <v>103</v>
+        <v>101</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
@@ -1376,6 +1395,9 @@
       <c r="A39" t="s">
         <v>60</v>
       </c>
+      <c r="B39" s="1" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
@@ -1428,7 +1450,7 @@
         <v>69</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
@@ -1486,6 +1508,9 @@
       <c r="A58" t="s">
         <v>79</v>
       </c>
+      <c r="B58" s="1" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
@@ -1501,55 +1526,70 @@
       <c r="A61" t="s">
         <v>82</v>
       </c>
+      <c r="B61">
+        <v>2</v>
+      </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>83</v>
       </c>
+      <c r="B62">
+        <v>1</v>
+      </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>84</v>
       </c>
+      <c r="B63" s="1" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B69">
+        <v>4100</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>92</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Giant Revolt X pro 1 long 2025.xlsx
+++ b/data/gravel/Giant Revolt X pro 1 long 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CD87513-1CDC-8F4D-B81B-BCF07AA38BA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D0722B6-53B0-2E4D-A9C9-37EF6C939B72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11060" yWindow="1320" windowWidth="26480" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="27120" yWindow="-23240" windowWidth="26480" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -334,9 +334,6 @@
     <t>internal</t>
   </si>
   <si>
-    <t>usd</t>
-  </si>
-  <si>
     <t>suspension</t>
   </si>
   <si>
@@ -347,6 +344,9 @@
   </si>
   <si>
     <t>https://www.giant-bicycles.com/discover/en-us/gravel-cycling/gravel/revolt-x</t>
+  </si>
+  <si>
+    <t>USD</t>
   </si>
 </sst>
 </file>
@@ -729,7 +729,7 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -1372,7 +1372,7 @@
         <v>101</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
@@ -1424,6 +1424,9 @@
       <c r="A43" t="s">
         <v>64</v>
       </c>
+      <c r="B43">
+        <v>40</v>
+      </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
@@ -1450,7 +1453,7 @@
         <v>69</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
@@ -1543,7 +1546,7 @@
         <v>84</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
@@ -1589,7 +1592,7 @@
         <v>92</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Giant Revolt X pro 1 long 2025.xlsx
+++ b/data/gravel/Giant Revolt X pro 1 long 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D0722B6-53B0-2E4D-A9C9-37EF6C939B72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88518669-BF2D-8643-A0E4-DC8EF22320AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="27120" yWindow="-23240" windowWidth="26480" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="110">
   <si>
     <t>brand</t>
   </si>
@@ -347,6 +347,9 @@
   </si>
   <si>
     <t>USD</t>
+  </si>
+  <si>
+    <t>https://images2.giant-bicycles.com/b_white%2Cc_pad%2Ch_400%2Cq_80%2Cw_600/neo58vnw944duajdacmp/MY24RevoltXAdvancedPro0_ColorAKelpForest.jpg</t>
   </si>
 </sst>
 </file>
@@ -732,6 +735,11 @@
         <v>107</v>
       </c>
     </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>109</v>
+      </c>
+    </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>8</v>

--- a/data/gravel/Giant Revolt X pro 1 long 2025.xlsx
+++ b/data/gravel/Giant Revolt X pro 1 long 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88518669-BF2D-8643-A0E4-DC8EF22320AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A489207-8391-674E-B895-E51C032F13FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="27120" yWindow="-23240" windowWidth="26480" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="112">
   <si>
     <t>brand</t>
   </si>
@@ -350,6 +350,12 @@
   </si>
   <si>
     <t>https://images2.giant-bicycles.com/b_white%2Cc_pad%2Ch_400%2Cq_80%2Cw_600/neo58vnw944duajdacmp/MY24RevoltXAdvancedPro0_ColorAKelpForest.jpg</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Dajia, Taichung, Taiwan</t>
   </si>
 </sst>
 </file>
@@ -689,7 +695,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H71"/>
+  <dimension ref="A1:H72"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1603,6 +1609,14 @@
         <v>108</v>
       </c>
     </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>110</v>
+      </c>
+      <c r="B72" t="s">
+        <v>111</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Giant Revolt X pro 1 long 2025.xlsx
+++ b/data/gravel/Giant Revolt X pro 1 long 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A489207-8391-674E-B895-E51C032F13FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E905917-AFFD-5E4B-B9E5-ECEA7C728510}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="118">
   <si>
     <t>brand</t>
   </si>
@@ -356,6 +356,24 @@
   </si>
   <si>
     <t>Dajia, Taichung, Taiwan</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -695,7 +713,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H72"/>
+  <dimension ref="A1:H78"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1464,156 +1482,186 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>69</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>70</v>
+        <v>113</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>71</v>
-      </c>
-      <c r="B50">
-        <v>30.9</v>
+        <v>114</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>72</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>73</v>
+        <v>116</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>74</v>
+        <v>117</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>75</v>
+        <v>69</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>77</v>
+        <v>71</v>
+      </c>
+      <c r="B56">
+        <v>30.9</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>78</v>
+        <v>72</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>79</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>103</v>
+        <v>73</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>82</v>
-      </c>
-      <c r="B61">
-        <v>2</v>
+        <v>76</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>83</v>
-      </c>
-      <c r="B62">
-        <v>1</v>
+        <v>77</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>84</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>85</v>
+        <v>79</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>88</v>
+        <v>82</v>
+      </c>
+      <c r="B67">
+        <v>2</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>89</v>
+        <v>83</v>
+      </c>
+      <c r="B68">
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>90</v>
-      </c>
-      <c r="B69">
-        <v>4100</v>
+        <v>84</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>92</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>108</v>
+        <v>86</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>90</v>
+      </c>
+      <c r="B75">
+        <v>4100</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>92</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
         <v>110</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B78" t="s">
         <v>111</v>
       </c>
     </row>

--- a/data/gravel/Giant Revolt X pro 1 long 2025.xlsx
+++ b/data/gravel/Giant Revolt X pro 1 long 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11130"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E905917-AFFD-5E4B-B9E5-ECEA7C728510}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB3E1133-6A75-1940-A6EC-2771A76E838B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="117">
   <si>
     <t>brand</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>model_year</t>
-  </si>
-  <si>
-    <t>2023</t>
   </si>
   <si>
     <t>input_date</t>
@@ -739,13 +736,13 @@
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
-        <v>5</v>
+      <c r="B3">
+        <v>2025</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" s="2">
         <v>45888</v>
@@ -753,57 +750,57 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C8" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>10</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>11</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>12</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>13</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>14</v>
-      </c>
-      <c r="H8" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
         <v>16</v>
-      </c>
-      <c r="B9" t="s">
-        <v>17</v>
       </c>
       <c r="C9">
         <v>430</v>
@@ -826,10 +823,10 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
         <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
       </c>
       <c r="C10">
         <v>73.900000000000006</v>
@@ -852,10 +849,10 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s">
         <v>20</v>
-      </c>
-      <c r="B11" t="s">
-        <v>21</v>
       </c>
       <c r="C11">
         <v>543</v>
@@ -878,10 +875,10 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" t="s">
         <v>22</v>
-      </c>
-      <c r="B12" t="s">
-        <v>23</v>
       </c>
       <c r="C12">
         <v>90</v>
@@ -904,10 +901,10 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" t="s">
         <v>24</v>
-      </c>
-      <c r="B13" t="s">
-        <v>25</v>
       </c>
       <c r="C13">
         <v>70.400000000000006</v>
@@ -930,10 +927,10 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" t="s">
         <v>26</v>
-      </c>
-      <c r="B14" t="s">
-        <v>27</v>
       </c>
       <c r="C14">
         <v>45</v>
@@ -956,10 +953,10 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" t="s">
         <v>28</v>
-      </c>
-      <c r="B15" t="s">
-        <v>29</v>
       </c>
       <c r="C15">
         <v>83.7</v>
@@ -982,10 +979,10 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" t="s">
         <v>30</v>
-      </c>
-      <c r="B16" t="s">
-        <v>31</v>
       </c>
       <c r="C16">
         <v>1033</v>
@@ -1008,10 +1005,10 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" t="s">
         <v>32</v>
-      </c>
-      <c r="B17" t="s">
-        <v>33</v>
       </c>
       <c r="C17">
         <v>435</v>
@@ -1034,10 +1031,10 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" t="s">
         <v>34</v>
-      </c>
-      <c r="B18" t="s">
-        <v>35</v>
       </c>
       <c r="C18">
         <v>69</v>
@@ -1060,10 +1057,10 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" t="s">
         <v>36</v>
-      </c>
-      <c r="B19" t="s">
-        <v>37</v>
       </c>
       <c r="C19">
         <v>549</v>
@@ -1086,10 +1083,10 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" t="s">
         <v>38</v>
-      </c>
-      <c r="B20" t="s">
-        <v>39</v>
       </c>
       <c r="C20">
         <v>386</v>
@@ -1112,10 +1109,10 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" t="s">
         <v>40</v>
-      </c>
-      <c r="B21" t="s">
-        <v>41</v>
       </c>
       <c r="C21">
         <v>726</v>
@@ -1138,10 +1135,10 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" t="s">
         <v>42</v>
-      </c>
-      <c r="B22" t="s">
-        <v>43</v>
       </c>
       <c r="C22">
         <v>440</v>
@@ -1164,10 +1161,10 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" t="s">
         <v>44</v>
-      </c>
-      <c r="B23" t="s">
-        <v>45</v>
       </c>
       <c r="C23">
         <v>50</v>
@@ -1190,10 +1187,10 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" t="s">
         <v>46</v>
-      </c>
-      <c r="B24" t="s">
-        <v>47</v>
       </c>
       <c r="C24">
         <v>170</v>
@@ -1216,15 +1213,15 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>47</v>
+      </c>
+      <c r="B26" t="s">
         <v>48</v>
-      </c>
-      <c r="B26" t="s">
-        <v>49</v>
       </c>
       <c r="C26">
         <v>700</v>
@@ -1247,10 +1244,10 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B27" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C27">
         <v>435</v>
@@ -1273,10 +1270,10 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B28" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C28">
         <v>50</v>
@@ -1299,10 +1296,10 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B29" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C29">
         <v>53</v>
@@ -1325,10 +1322,10 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B30" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C30">
         <v>155</v>
@@ -1351,10 +1348,10 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B31" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C31">
         <v>163</v>
@@ -1377,63 +1374,63 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>54</v>
+      </c>
+      <c r="B33" t="s">
         <v>55</v>
-      </c>
-      <c r="B33" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>96</v>
+      </c>
+      <c r="B34" t="s">
         <v>97</v>
-      </c>
-      <c r="B34" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>98</v>
+      </c>
+      <c r="B35" t="s">
         <v>99</v>
-      </c>
-      <c r="B35" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>56</v>
+      </c>
+      <c r="B37" t="s">
         <v>57</v>
-      </c>
-      <c r="B37" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B40">
         <v>53</v>
@@ -1441,12 +1438,12 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B42">
         <v>40</v>
@@ -1454,7 +1451,7 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B43">
         <v>40</v>
@@ -1462,70 +1459,70 @@
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B56">
         <v>30.9</v>
@@ -1533,63 +1530,63 @@
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B67">
         <v>2</v>
@@ -1597,7 +1594,7 @@
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B68">
         <v>1</v>
@@ -1605,40 +1602,40 @@
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B75">
         <v>4100</v>
@@ -1646,23 +1643,23 @@
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
+        <v>109</v>
+      </c>
+      <c r="B78" t="s">
         <v>110</v>
-      </c>
-      <c r="B78" t="s">
-        <v>111</v>
       </c>
     </row>
   </sheetData>
